--- a/processed-data/04_snRNA-seq/35_sn_subcluster_marker_modeling/Astro/subtype_NOTES_Astro.xlsx
+++ b/processed-data/04_snRNA-seq/35_sn_subcluster_marker_modeling/Astro/subtype_NOTES_Astro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/04_snRNA-seq/35_sn_subcluster_marker_modeling/Astro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{5E0CC30D-8B8A-9C48-85CC-689D73F7D7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ABB3C60-F4C0-3143-92CF-21D46888F22B}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{5E0CC30D-8B8A-9C48-85CC-689D73F7D7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFE52668-3C9B-674D-8DA7-86AEC7E9FC09}"/>
   <bookViews>
-    <workbookView xWindow="9380" yWindow="1520" windowWidth="20060" windowHeight="14180" xr2:uid="{D80092CD-BA0F-7C4B-A6C5-BB4E3B9DC9CD}"/>
+    <workbookView xWindow="7180" yWindow="-17380" windowWidth="29580" windowHeight="16060" xr2:uid="{D80092CD-BA0F-7C4B-A6C5-BB4E3B9DC9CD}"/>
   </bookViews>
   <sheets>
     <sheet name="subtype_marker_summary_Astro" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
   <si>
     <t>cell_type</t>
   </si>
@@ -131,6 +131,18 @@
   </si>
   <si>
     <t>Interlaminar</t>
+  </si>
+  <si>
+    <t>Mathys et al. best match</t>
+  </si>
+  <si>
+    <t>DCLK1</t>
+  </si>
+  <si>
+    <t>GRM3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low cor </t>
   </si>
 </sst>
 </file>
@@ -672,6 +684,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -991,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14EAC8C7-4345-9445-9382-85DBD64F52FD}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="40.1640625" bestFit="1" customWidth="1"/>
@@ -1001,7 +1017,7 @@
     <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1029,8 +1045,11 @@
       <c r="I1" t="s">
         <v>29</v>
       </c>
+      <c r="J1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1058,8 +1077,11 @@
       <c r="I2" t="s">
         <v>33</v>
       </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1087,8 +1109,11 @@
       <c r="I3" t="s">
         <v>33</v>
       </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1116,8 +1141,11 @@
       <c r="I4" t="s">
         <v>33</v>
       </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1145,8 +1173,11 @@
       <c r="I5" t="s">
         <v>32</v>
       </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1170,6 +1201,9 @@
       </c>
       <c r="I6" t="s">
         <v>33</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
